--- a/seshop_books.xlsx
+++ b/seshop_books.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_Data_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83575937-EEB5-411B-B252-4D91ECC22D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E661245-EB6F-48A2-8A43-E6335F284C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>img_url</t>
   </si>
   <si>
-    <t>url</t>
+    <t>book_url</t>
   </si>
   <si>
     <t>price</t>
@@ -571,7 +571,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="137.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" customWidth="1"/>
     <col min="4" max="4" width="20.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.109375" bestFit="1" customWidth="1"/>
   </cols>

--- a/seshop_books.xlsx
+++ b/seshop_books.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,26 @@
           <t>published</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>author</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>isbn</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>format</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -472,6 +492,24 @@
       <c r="F2" s="1" t="n">
         <v>46325</v>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>['森 巧尚']</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9784798193052</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>B5変</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -498,6 +536,10 @@
       <c r="F3" s="1" t="n">
         <v>46164</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -524,6 +566,10 @@
       <c r="F4" s="1" t="n">
         <v>45967</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -550,6 +596,10 @@
       <c r="F5" s="1" t="n">
         <v>45946</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -576,6 +626,10 @@
       <c r="F6" s="1" t="n">
         <v>45874</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -602,6 +656,10 @@
       <c r="F7" s="1" t="n">
         <v>45798</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -628,6 +686,10 @@
       <c r="F8" s="1" t="n">
         <v>45791</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -654,6 +716,10 @@
       <c r="F9" s="1" t="n">
         <v>45530</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -680,6 +746,10 @@
       <c r="F10" s="1" t="n">
         <v>45513</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -706,6 +776,10 @@
       <c r="F11" s="1" t="n">
         <v>45468</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -732,6 +806,10 @@
       <c r="F12" s="1" t="n">
         <v>45467</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -758,6 +836,10 @@
       <c r="F13" s="1" t="n">
         <v>45463</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -784,6 +866,10 @@
       <c r="F14" s="1" t="n">
         <v>45460</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -810,6 +896,10 @@
       <c r="F15" s="1" t="n">
         <v>45455</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -836,6 +926,10 @@
       <c r="F16" s="1" t="n">
         <v>45432</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -862,6 +956,10 @@
       <c r="F17" s="1" t="n">
         <v>45432</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -888,6 +986,10 @@
       <c r="F18" s="1" t="n">
         <v>45393</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -914,6 +1016,10 @@
       <c r="F19" s="1" t="n">
         <v>45335</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -940,6 +1046,10 @@
       <c r="F20" s="1" t="n">
         <v>45252</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -966,6 +1076,10 @@
       <c r="F21" s="1" t="n">
         <v>45246</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -992,6 +1106,10 @@
       <c r="F22" s="1" t="n">
         <v>45142</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
